--- a/datasets/Dataset_S8_Seeded_run_stability.xlsx
+++ b/datasets/Dataset_S8_Seeded_run_stability.xlsx
@@ -62,7 +62,7 @@
     <t xml:space="preserve">S8-5. Core stress enrichment</t>
   </si>
   <si>
-    <t xml:space="preserve">Number of stress-coupled regulators among the top 15 by IC in each seeded run and in the representative network, with the hypergeometric test against a pool of 38 regulators of which 17 are stress-coupled.</t>
+    <t xml:space="preserve">Number of stress-related regulators among the top 15 by IC in each seeded run and in the representative network, with the hypergeometric test against a pool of 38 regulators of which 17 are stress-related.</t>
   </si>
   <si>
     <t xml:space="preserve">S8-6. Network recurrence</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">Range and median of the regulator's IC rank across the seeded runs in which it was ranked.</t>
   </si>
   <si>
-    <t xml:space="preserve">Stress_coupled</t>
+    <t xml:space="preserve">Stress_related</t>
   </si>
   <si>
     <t xml:space="preserve">Y if a stress role is assigned to the regulator in Dataset S6, N otherwise.</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">Expected_at_random</t>
   </si>
   <si>
-    <t xml:space="preserve">Stress-coupled regulators expected among 15 drawn at random from the pool, that is 15 x 17 / 38.</t>
+    <t xml:space="preserve">Stress-related regulators expected among 15 drawn at random from the pool, that is 15 x 17 / 38.</t>
   </si>
   <si>
     <t xml:space="preserve">Hypergeometric_p</t>
   </si>
   <si>
-    <t xml:space="preserve">One-sided probability of observing at least this many stress-coupled regulators by chance.</t>
+    <t xml:space="preserve">One-sided probability of observing at least this many stress-related regulators by chance.</t>
   </si>
   <si>
     <t xml:space="preserve">Edges_recurring_in_...</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">Run</t>
   </si>
   <si>
-    <t xml:space="preserve">Stress_coupled_in_top15</t>
+    <t xml:space="preserve">Stress_related_in_top15</t>
   </si>
   <si>
     <t xml:space="preserve">Significant_at_0.05</t>
